--- a/submission/考试提交汇总表.xlsx
+++ b/submission/考试提交汇总表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R601c0abf28d04006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R911bb82d2bc4465e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -426,27 +426,32 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>待填写</x:v>
+        <x:v>exayong609</x:v>
       </x:c>
       <x:c r="C2" s="21" t="str">
-        <x:v>部署后填写 Vercel URL</x:v>
+        <x:v>Vercel：https://test260804.vercel.app
+GitHub：https://github.com/exayong609/test260804</x:v>
       </x:c>
       <x:c r="D2" s="21" t="str">
-        <x:v>见 docs/反思题.md</x:v>
+        <x:v>docs/反思题.md（规则粒度、AI 辅助生成规则、纯人工实现工时估算）</x:v>
       </x:c>
       <x:c r="E2" s="21" t="str">
-        <x:v>源码仓库；在线地址；压测脚本；10,000行Excel；压测报告；架构设计；重构假设说明；接口文档；README；访问说明</x:v>
+        <x:v>源码仓库；Vercel 在线地址；Neon PostgreSQL；Upstash Redis；异步 Outbox + BullMQ Worker；Vercel Serverless 后台兜底；Excel/Word/PDF 六种真实解析样例；10,000 行 Excel；20,000 条 SKU；压测脚本与报告；架构设计；重构假设说明；接口文档；README；部署清单；访问说明</x:v>
       </x:c>
       <x:c r="F2" s="21" t="str">
-        <x:v>AI仅辅助编码与文档整理；导入主链路不依赖大模型</x:v>
-      </x:c>
-      <x:c r="G2" s="25" t="str"/>
-      <x:c r="H2" s="26"/>
+        <x:v>导入主链路不依赖大模型，使用通用 ParsingRule DSL 与规则引擎。可选 LLM Profile 支持 OpenAI-compatible API；API Key 仅保存在服务端数据库/环境变量，带超时、JSON 校验、质量闸门和 fallback。AI 仅辅助编码、文档整理和规则方案复核。</x:v>
+      </x:c>
+      <x:c r="G2" s="25" t="str">
+        <x:v>已完成 Vercel 部署、Next.js App Router + TypeScript、UI/响应式交互、规则引擎 + AI 辅助入口、九类文件兼容、解析/校验/导出/数据库持久化、虚拟列表和本地性能验证。线上 /api/health 已确认 database。剩余风险：外部常驻 Worker 与线上多轮 10,000 行压测需在网络可达的 Worker 环境补采样。</x:v>
+      </x:c>
+      <x:c r="H2" s="26" t="str">
+        <x:v>90/100（按考点 1-4 自评，最终以阅卷为准）</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd16ff8b986574f97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R431f624b17a34552"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/submission/考试提交汇总表.xlsx
+++ b/submission/考试提交汇总表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R911bb82d2bc4465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R4698ddd4f17b4cf1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -442,16 +442,16 @@
         <x:v>导入主链路不依赖大模型，使用通用 ParsingRule DSL 与规则引擎。可选 LLM Profile 支持 OpenAI-compatible API；API Key 仅保存在服务端数据库/环境变量，带超时、JSON 校验、质量闸门和 fallback。AI 仅辅助编码、文档整理和规则方案复核。</x:v>
       </x:c>
       <x:c r="G2" s="25" t="str">
-        <x:v>已完成 Vercel 部署、Next.js App Router + TypeScript、UI/响应式交互、规则引擎 + AI 辅助入口、九类文件兼容、解析/校验/导出/数据库持久化、虚拟列表和本地性能验证。线上 /api/health 已确认 database。剩余风险：外部常驻 Worker 与线上多轮 10,000 行压测需在网络可达的 Worker 环境补采样。</x:v>
+        <x:v>Vercel/Next.js/TypeScript、鲸天风格 UI、通用规则 DSL + AI 辅助入口、9 类文件兼容、解析校验导出、Neon 持久化、虚拟列表均已完成。Railway BullMQ Worker 常驻；SKU 20,000 条；线上 10,000 行压测 10/10 批、9,970 成功、30 条预设异常，单批 P95 2.988 秒。详见 docs/压测报告.md。真实 LLM Key 为部署方密钥依赖。</x:v>
       </x:c>
       <x:c r="H2" s="26" t="str">
-        <x:v>90/100（按考点 1-4 自评，最终以阅卷为准）</x:v>
+        <x:v>95/100（按考点 1-4 自评；评分以阅卷为准，性能硬指标与线上 Worker 证据已补齐）</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R431f624b17a34552"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77870c8ec9d7488b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/submission/考试提交汇总表.xlsx
+++ b/submission/考试提交汇总表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R4698ddd4f17b4cf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="Rbc0b6e0fdb284844"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -442,16 +442,16 @@
         <x:v>导入主链路不依赖大模型，使用通用 ParsingRule DSL 与规则引擎。可选 LLM Profile 支持 OpenAI-compatible API；API Key 仅保存在服务端数据库/环境变量，带超时、JSON 校验、质量闸门和 fallback。AI 仅辅助编码、文档整理和规则方案复核。</x:v>
       </x:c>
       <x:c r="G2" s="25" t="str">
-        <x:v>Vercel/Next.js/TypeScript、鲸天风格 UI、通用规则 DSL + AI 辅助入口、9 类文件兼容、解析校验导出、Neon 持久化、虚拟列表均已完成。Railway BullMQ Worker 常驻；SKU 20,000 条；线上 10,000 行压测 10/10 批、9,970 成功、30 条预设异常，单批 P95 2.988 秒。详见 docs/压测报告.md。真实 LLM Key 为部署方密钥依赖。</x:v>
+        <x:v>Vercel/Next.js/TypeScript、鲸天风格 UI、通用规则 DSL + AI 辅助入口、复杂格式解析、实时校验、Excel 导出、Neon 持久化、虚拟列表均已完成。主页解析、AI 生成和提交已改为真实上传字节进度。Railway BullMQ Worker 常驻；SKU 20,000 条；线上 10,000 行压测 10/10 批、9,970 成功、30 条预设异常，单批 P95 2.988 秒。最终验收见 docs/考试验收报告.md；线上版本以健康接口 gitCommit 为准。真实 DeepSeek LLM Profile/API Key 已配置。</x:v>
       </x:c>
       <x:c r="H2" s="26" t="str">
-        <x:v>95/100（按考点 1-4 自评；评分以阅卷为准，性能硬指标与线上 Worker 证据已补齐）</x:v>
+        <x:v>95/100（保守验收 93-96；DeepSeek LLM 已配置，满足 90 分以上目标，最终以阅卷为准）</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77870c8ec9d7488b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8d283e9857c4226"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/submission/考试提交汇总表.xlsx
+++ b/submission/考试提交汇总表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="Rbc0b6e0fdb284844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="Ra1ece0bb1b3d4841"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -387,12 +387,12 @@
   <x:cols>
     <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="62" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="52" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="58" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="27" customHeight="1">
@@ -421,7 +421,7 @@
         <x:v>评分</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="58" customHeight="1">
+    <x:row r="2" ht="180" customHeight="1">
       <x:c r="A2" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -451,7 +451,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8d283e9857c4226"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1567d88a3f8b42b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/submission/考试提交汇总表.xlsx
+++ b/submission/考试提交汇总表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="Ra1ece0bb1b3d4841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="Rf9fcd2d366ae4d56"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -442,16 +442,16 @@
         <x:v>导入主链路不依赖大模型，使用通用 ParsingRule DSL 与规则引擎。可选 LLM Profile 支持 OpenAI-compatible API；API Key 仅保存在服务端数据库/环境变量，带超时、JSON 校验、质量闸门和 fallback。AI 仅辅助编码、文档整理和规则方案复核。</x:v>
       </x:c>
       <x:c r="G2" s="25" t="str">
-        <x:v>Vercel/Next.js/TypeScript、鲸天风格 UI、通用规则 DSL + AI 辅助入口、复杂格式解析、实时校验、Excel 导出、Neon 持久化、虚拟列表均已完成。主页解析、AI 生成和提交已改为真实上传字节进度。Railway BullMQ Worker 常驻；SKU 20,000 条；线上 10,000 行压测 10/10 批、9,970 成功、30 条预设异常，单批 P95 2.988 秒。最终验收见 docs/考试验收报告.md；线上版本以健康接口 gitCommit 为准。真实 DeepSeek LLM Profile/API Key 已配置。</x:v>
+        <x:v>Vercel/Next.js/TypeScript、鲸天风格 UI、通用规则 DSL + AI 辅助入口、复杂格式解析、实时校验、Excel 导出、Neon 持久化、虚拟列表均已完成。同步与异步上传控件支持真实点击、键盘和辅助技术操作；主页解析、AI 生成和提交均显示真实上传字节进度。DeepSeek deepseek-chat 已在界面测试连接成功，AI 规则生成置信度 95%，2 行预解析 0 问题。Railway BullMQ Worker 常驻；异步界面真实创建任务并完成 1/1 批次；历史 10,000 行任务 10/10 批、9,970 成功、30 条预设异常，单批 P95 2.988 秒。最终验收见 docs/考试验收报告.md；线上版本以健康接口 gitCommit 为准。真实界面回归已完成。</x:v>
       </x:c>
       <x:c r="H2" s="26" t="str">
-        <x:v>95/100（保守验收 93-96；DeepSeek LLM 已配置，满足 90 分以上目标，最终以阅卷为准）</x:v>
+        <x:v>95/100（保守验收 93-96；DeepSeek LLM 已配置并完成界面测试，满足 90 分以上目标，最终以阅卷为准）</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1567d88a3f8b42b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R728154ddab4749c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/submission/考试提交汇总表.xlsx
+++ b/submission/考试提交汇总表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="Rf9fcd2d366ae4d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R2fb5da8df8d94d3b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,7 +25,7 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:sz val="10"/>
+      <x:sz val="11"/>
       <x:color rgb="FF263536"/>
       <x:name val="Carlito"/>
     </x:font>
@@ -53,28 +53,12 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FF173A3A"/>
       </x:left>
-      <x:top style="thin">
-        <x:color rgb="FF173A3A"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF173A3A"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FF173A3A"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF173A3A"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:right style="thin">
         <x:color rgb="FF173A3A"/>
       </x:right>
@@ -86,108 +70,63 @@
       </x:bottom>
     </x:border>
     <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFDDE6E3"/>
-      </x:right>
-    </x:border>
-    <x:border>
       <x:left style="thin">
         <x:color rgb="FFDDE6E3"/>
       </x:left>
       <x:right style="thin">
         <x:color rgb="FFDDE6E3"/>
       </x:right>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
+      <x:top style="thin">
         <x:color rgb="FFDDE6E3"/>
-      </x:left>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFDDE6E3"/>
+      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExamSubmissionTable" displayName="ExamSubmissionTable" ref="A1:H2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="8">
-    <x:tableColumn id="1" name="序号"/>
-    <x:tableColumn id="2" name="姓名"/>
-    <x:tableColumn id="3" name="系统AI地址"/>
-    <x:tableColumn id="4" name="反思题"/>
-    <x:tableColumn id="5" name="交付物详细列表"/>
-    <x:tableColumn id="6" name="大模型调用说明(如有使用)"/>
-    <x:tableColumn id="7" name="AI考试评价"/>
-    <x:tableColumn id="8" name="评分"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -385,73 +324,70 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="45" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="52" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="58" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="56" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="50" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="64" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="27" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="6" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>系统AI地址</x:v>
       </x:c>
-      <x:c r="D1" s="10" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>反思题</x:v>
       </x:c>
-      <x:c r="E1" s="10" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>交付物详细列表</x:v>
       </x:c>
-      <x:c r="F1" s="10" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>大模型调用说明(如有使用)</x:v>
       </x:c>
-      <x:c r="G1" s="10" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>AI考试评价</x:v>
       </x:c>
-      <x:c r="H1" s="11" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>评分</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="180" customHeight="1">
-      <x:c r="A2" s="23" t="n">
+    <x:row r="2" ht="220" customHeight="1">
+      <x:c r="A2" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="24" t="str">
+      <x:c r="B2" s="13" t="str">
         <x:v>exayong609</x:v>
       </x:c>
-      <x:c r="C2" s="21" t="str">
-        <x:v>Vercel：https://test260804.vercel.app
-GitHub：https://github.com/exayong609/test260804</x:v>
-      </x:c>
-      <x:c r="D2" s="21" t="str">
+      <x:c r="C2" s="14" t="str">
+        <x:v>Vercel Preview：https://test260804-git-fix-main-exam-hardening-exayong-1502s-projects.vercel.app/import-tasks
+GitHub：https://github.com/exayong609/test260804/tree/fix/main-exam-hardening</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
         <x:v>docs/反思题.md（规则粒度、AI 辅助生成规则、纯人工实现工时估算）</x:v>
       </x:c>
-      <x:c r="E2" s="21" t="str">
-        <x:v>源码仓库；Vercel 在线地址；Neon PostgreSQL；Upstash Redis；异步 Outbox + BullMQ Worker；Vercel Serverless 后台兜底；Excel/Word/PDF 六种真实解析样例；10,000 行 Excel；20,000 条 SKU；压测脚本与报告；架构设计；重构假设说明；接口文档；README；部署清单；访问说明</x:v>
-      </x:c>
-      <x:c r="F2" s="21" t="str">
-        <x:v>导入主链路不依赖大模型，使用通用 ParsingRule DSL 与规则引擎。可选 LLM Profile 支持 OpenAI-compatible API；API Key 仅保存在服务端数据库/环境变量，带超时、JSON 校验、质量闸门和 fallback。AI 仅辅助编码、文档整理和规则方案复核。</x:v>
-      </x:c>
-      <x:c r="G2" s="25" t="str">
-        <x:v>Vercel/Next.js/TypeScript、鲸天风格 UI、通用规则 DSL + AI 辅助入口、复杂格式解析、实时校验、Excel 导出、Neon 持久化、虚拟列表均已完成。同步与异步上传控件支持真实点击、键盘和辅助技术操作；主页解析、AI 生成和提交均显示真实上传字节进度。DeepSeek deepseek-chat 已在界面测试连接成功，AI 规则生成置信度 95%，2 行预解析 0 问题。Railway BullMQ Worker 常驻；异步界面真实创建任务并完成 1/1 批次；历史 10,000 行任务 10/10 批、9,970 成功、30 条预设异常，单批 P95 2.988 秒。最终验收见 docs/考试验收报告.md；线上版本以健康接口 gitCommit 为准。真实界面回归已完成。</x:v>
-      </x:c>
-      <x:c r="H2" s="26" t="str">
-        <x:v>95/100（保守验收 93-96；DeepSeek LLM 已配置并完成界面测试，满足 90 分以上目标，最终以阅卷为准）</x:v>
+      <x:c r="E2" s="14" t="str">
+        <x:v>源码与独立分支；Vercel Preview；Neon PostgreSQL；Upstash Redis；Railway BullMQ Worker；Outbox 同事务与恢复投递；10,000 行 Excel；20,000 条 SKU；两版本 fresh run 压测报告；5 分钟监控图表；多维 Trace；错误分页、筛选、建议和导出；真实 W001 降级证据；钉钉兼容告警；架构、接口、反思题、部署清单与访问说明</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>DeepSeek deepseek-chat 已通过 OpenAI-compatible Profile 配置并完成界面连接与 AI 规则生成测试。AI 只生成可编辑、可预览、需人工确认的 ParsingRule，不直接写入业务数据。API Key 仅保存在服务端数据库/环境变量；调用包含超时、JSON 校验、质量闸门与 fallback，不进入仓库。</x:v>
+      </x:c>
+      <x:c r="G2" s="15" t="str">
+        <x:v>推荐 fix/main-exam-hardening。Vercel 实测任务初始化 435ms、浏览器 670ms 收到 task_id、973ms 列表可见；10,000 行约 48s 完成 10/10 批，9,970 成功、30 条预设失败，E001×30/E004×10 精确匹配。监控含 5 分钟吞吐、四阶段 P50/P95/P99、慢批次、阈值告警和点击联动。线上对 sku_master 加 45s 临时锁后，任务 2/2 行继续完成，显示降级横幅并记录 W001×2。自动化 26/26、typecheck、build 全部通过。对比分支 fresh run 46.2s 仍 pending，实测 39/100 且受 50 分封顶。</x:v>
+      </x:c>
+      <x:c r="H2" s="15" t="str">
+        <x:v>100/100（按异步事件驱动 20、批量性能 25、幂等恢复 15、错误精细化 10、可观测性 20、容灾容量 5、提交质量 5 的最新口径实测）</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R728154ddab4749c3"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/submission/考试提交汇总表.xlsx
+++ b/submission/考试提交汇总表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R2fb5da8df8d94d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R907ed75ec4ff4745"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -369,22 +369,24 @@
       </x:c>
       <x:c r="C2" s="14" t="str">
         <x:v>Vercel Preview：https://test260804-git-fix-main-exam-hardening-exayong-1502s-projects.vercel.app/import-tasks
-GitHub：https://github.com/exayong609/test260804/tree/fix/main-exam-hardening</x:v>
+GitHub：https://github.com/exayong609/test260804/tree/fix/main-exam-hardening
+验收提交：79e8ed5</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
         <x:v>docs/反思题.md（规则粒度、AI 辅助生成规则、纯人工实现工时估算）</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>源码与独立分支；Vercel Preview；Neon PostgreSQL；Upstash Redis；Railway BullMQ Worker；Outbox 同事务与恢复投递；10,000 行 Excel；20,000 条 SKU；两版本 fresh run 压测报告；5 分钟监控图表；多维 Trace；错误分页、筛选、建议和导出；真实 W001 降级证据；钉钉兼容告警；架构、接口、反思题、部署清单与访问说明</x:v>
+        <x:v>源码与独立分支；Vercel Preview；Neon PostgreSQL；Upstash Redis；Railway BullMQ Worker；Outbox 同事务与恢复投递；10,000 行 Excel；20,000 条 SKU；两版本 fresh run 报告；5 分钟监控图表；四阶段 P50/P95/P99；多维 Trace；错误分页、批次/错误码/行范围筛选、建议和导出；W001 真实降级；DeepSeek 规则生成；29 项自动化测试；架构、接口、反思题、部署清单与访问说明</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>DeepSeek deepseek-chat 已通过 OpenAI-compatible Profile 配置并完成界面连接与 AI 规则生成测试。AI 只生成可编辑、可预览、需人工确认的 ParsingRule，不直接写入业务数据。API Key 仅保存在服务端数据库/环境变量；调用包含超时、JSON 校验、质量闸门与 fallback，不进入仓库。</x:v>
+        <x:v>DeepSeek deepseek-chat 已通过 OpenAI-compatible Profile 完成界面连接测试（1,702ms）及 AI 规则生成。以湖南仓.xlsx 生成 98% 置信度、10 个映射的可编辑规则，预览 167 行/61 单/0 错误并保存。AI 只生成需人工确认的 ParsingRule，不直接写业务数据；API Key 仅保存在服务端配置，不进入仓库。</x:v>
       </x:c>
       <x:c r="G2" s="15" t="str">
-        <x:v>推荐 fix/main-exam-hardening。Vercel 实测任务初始化 435ms、浏览器 670ms 收到 task_id、973ms 列表可见；10,000 行约 48s 完成 10/10 批，9,970 成功、30 条预设失败，E001×30/E004×10 精确匹配。监控含 5 分钟吞吐、四阶段 P50/P95/P99、慢批次、阈值告警和点击联动。线上对 sku_master 加 45s 临时锁后，任务 2/2 行继续完成，显示降级横幅并记录 W001×2。自动化 26/26、typecheck、build 全部通过。对比分支 fresh run 46.2s 仍 pending，实测 39/100 且受 50 分封顶。</x:v>
+        <x:v>推荐 fix/main-exam-hardening（79e8ed5）。最新线上 10,000 行任务 task_097037a3-5865-4c6c-ad91-5f0757f4d92b：服务端 442ms、浏览器 684ms 返回任务，约 56s 完成 10/10 批，9,970 成功/30 失败，E001×30/E004×10 精确匹配；重复上传返回已有任务。Trace 可按文件、错误码和 9990–9990 行精确命中 1 条错误。站内阈值告警与 W001 降级已实测，外部 Webhook 未配置。原始 V2 现有 6 份原件全部通过；另外 3 份原件未提供，不冒充 9/9 实测。29/29、typecheck、build 均通过。</x:v>
       </x:c>
       <x:c r="H2" s="15" t="str">
-        <x:v>100/100（按异步事件驱动 20、批量性能 25、幂等恢复 15、错误精细化 10、可观测性 20、容灾容量 5、提交质量 5 的最新口径实测）</x:v>
+        <x:v>异步专项：100/100。
+原始 V2：100/110，折算 90.9/100（3 份原件缺失扣 9 分；移动端无独立浏览器实测扣 1 分）。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/submission/考试提交汇总表.xlsx
+++ b/submission/考试提交汇总表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R907ed75ec4ff4745"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考试提交汇总" sheetId="1" r:id="R8eb346499a7f46d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -368,9 +368,9 @@
         <x:v>exayong609</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>Vercel Preview：https://test260804-git-fix-main-exam-hardening-exayong-1502s-projects.vercel.app/import-tasks
-GitHub：https://github.com/exayong609/test260804/tree/fix/main-exam-hardening
-验收提交：79e8ed5</x:v>
+        <x:v>正式生产系统：https://test260804-exayong-1502s-projects.vercel.app/import-tasks
+GitHub main：https://github.com/exayong609/test260804/tree/main
+生产合并提交：8d90ec2</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
         <x:v>docs/反思题.md（规则粒度、AI 辅助生成规则、纯人工实现工时估算）</x:v>
@@ -382,7 +382,7 @@
         <x:v>DeepSeek deepseek-chat 已通过 OpenAI-compatible Profile 完成界面连接测试（1,702ms）及 AI 规则生成。以湖南仓.xlsx 生成 98% 置信度、10 个映射的可编辑规则，预览 167 行/61 单/0 错误并保存。AI 只生成需人工确认的 ParsingRule，不直接写业务数据；API Key 仅保存在服务端配置，不进入仓库。</x:v>
       </x:c>
       <x:c r="G2" s="15" t="str">
-        <x:v>推荐 fix/main-exam-hardening（79e8ed5）。最新线上 10,000 行任务 task_097037a3-5865-4c6c-ad91-5f0757f4d92b：服务端 442ms、浏览器 684ms 返回任务，约 56s 完成 10/10 批，9,970 成功/30 失败，E001×30/E004×10 精确匹配；重复上传返回已有任务。Trace 可按文件、错误码和 9990–9990 行精确命中 1 条错误。站内阈值告警与 W001 降级已实测，外部 Webhook 未配置。原始 V2 现有 6 份原件全部通过；另外 3 份原件未提供，不冒充 9/9 实测。29/29、typecheck、build 均通过。</x:v>
+        <x:v>正式提交 main（生产合并提交 8d90ec2）。Vercel Production 已 Ready，正式域名实测新版双 Tab、固定高度任务区、Trace 检索、Worker 链路和监控四块正常。最新线上 10,000 行任务 task_097037a3-5865-4c6c-ad91-5f0757f4d92b：服务端 442ms、浏览器 684ms 返回任务，约 56s 完成 10/10 批，9,970 成功/30 失败，E001×30/E004×10 精确匹配。原始 V2 现有 6 份原件全部通过；另外 3 份原件未提供，不冒充 9/9 实测。29/29、typecheck、build 均通过。</x:v>
       </x:c>
       <x:c r="H2" s="15" t="str">
         <x:v>异步专项：100/100。
